--- a/facit/CodeSystem-kontakttyp.xlsx
+++ b/facit/CodeSystem-kontakttyp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T14:14:36+00:00</t>
+    <t>2026-10-28T14:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
